--- a/test/questionnaire_answers/demographic_questions.xlsx
+++ b/test/questionnaire_answers/demographic_questions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cocac\Desktop\UNI\AAU\MED7\Sound and Music Perception and Cognition\Miniproject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cocac\OneDrive\Documentos\GitHub\SMPC-miniproject\test\questionnaire_answers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F060CB4-9607-4870-B89C-06D64D6CDBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABA4437-F649-46FC-80DC-FAB9EA36376F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2940" yWindow="2592" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
   <si>
     <t>ID</t>
   </si>
@@ -528,20 +528,68 @@
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
+      <c r="B11">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
+      </c>
+      <c r="B12">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">

--- a/test/questionnaire_answers/demographic_questions.xlsx
+++ b/test/questionnaire_answers/demographic_questions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cocac\OneDrive\Documentos\GitHub\SMPC-miniproject\test\questionnaire_answers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6450fa75d544e033/Documentos/GitHub/SMPC-miniproject/test/questionnaire_answers/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABA4437-F649-46FC-80DC-FAB9EA36376F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{CABA4437-F649-46FC-80DC-FAB9EA36376F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7944D73A-E012-468A-B16B-60285BBC459B}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2592" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="7">
   <si>
     <t>ID</t>
   </si>
@@ -596,15 +596,51 @@
       <c r="A13">
         <v>12</v>
       </c>
+      <c r="B13">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
+      <c r="B14">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
+      </c>
+      <c r="B15">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
